--- a/data/user_mapping.xlsx
+++ b/data/user_mapping.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -437,6 +437,18 @@
       <c r="B2" t="inlineStr">
         <is>
           <t>19837229903@163.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>denningskat437</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>denningskat437@gmail.com</t>
         </is>
       </c>
     </row>
